--- a/Assets/SimpleSolitaire/Data/Levels.xlsx
+++ b/Assets/SimpleSolitaire/Data/Levels.xlsx
@@ -89,10 +89,10 @@
     <t>是否游戏结算广告</t>
   </si>
   <si>
-    <t>1|12|3|4</t>
-  </si>
-  <si>
-    <t>1|2|3|4|5</t>
+    <t>2|3|4|5</t>
+  </si>
+  <si>
+    <t>1|2|3|4|5|6|7|8</t>
   </si>
 </sst>
 </file>
@@ -708,12 +708,9 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1250,7 +1247,7 @@
     <col min="2" max="2" width="16.0769230769231" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.6923076923077" style="1" customWidth="1"/>
     <col min="4" max="4" width="10.3076923076923" customWidth="1"/>
-    <col min="5" max="5" width="12.8461538461538" customWidth="1"/>
+    <col min="5" max="5" width="34.6057692307692" customWidth="1"/>
     <col min="6" max="6" width="7.30769230769231" customWidth="1"/>
     <col min="7" max="7" width="10.3076923076923" customWidth="1"/>
     <col min="8" max="10" width="20" customWidth="1"/>
@@ -1301,7 +1298,7 @@
       <c r="D2" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="F2" t="s">
